--- a/documentation/raw_data_analysis_01.xlsx
+++ b/documentation/raw_data_analysis_01.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T5"/>
+  <dimension ref="A1:T4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -750,70 +750,6 @@
         <v>5660</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>Books</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="n">
-        <v>29475453</v>
-      </c>
-      <c r="C5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>29475449</v>
-      </c>
-      <c r="F5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" s="2" t="n">
-        <v>967</v>
-      </c>
-      <c r="J5" s="2" t="n">
-        <v>1316085</v>
-      </c>
-      <c r="K5" s="2" t="n">
-        <v>1080897</v>
-      </c>
-      <c r="L5" s="2" t="n">
-        <v>2054057</v>
-      </c>
-      <c r="M5" s="2" t="n">
-        <v>4632932</v>
-      </c>
-      <c r="N5" s="2" t="n">
-        <v>20391478</v>
-      </c>
-      <c r="O5" s="2" t="n">
-        <v>12470368303</v>
-      </c>
-      <c r="P5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="2" t="n">
-        <v>37878</v>
-      </c>
-      <c r="R5" s="2" t="n">
-        <v>2197204101</v>
-      </c>
-      <c r="S5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" s="2" t="n">
-        <v>6192</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -825,7 +761,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -979,37 +915,6 @@
         <v>2199</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>Books</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="n">
-        <v>967</v>
-      </c>
-      <c r="C5" s="2" t="n">
-        <v>1116644</v>
-      </c>
-      <c r="D5" s="2" t="n">
-        <v>4401050</v>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>3592472</v>
-      </c>
-      <c r="F5" s="2" t="n">
-        <v>13777789</v>
-      </c>
-      <c r="G5" s="2" t="n">
-        <v>3451764</v>
-      </c>
-      <c r="H5" s="2" t="n">
-        <v>3025744</v>
-      </c>
-      <c r="I5" s="2" t="n">
-        <v>109019</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1021,7 +926,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1346,96 +1251,6 @@
         <v>1208360</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>Books</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>Train</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="n">
-        <v>20632814</v>
-      </c>
-      <c r="D11" s="2" t="n">
-        <v>838284</v>
-      </c>
-      <c r="E11" s="2" t="n">
-        <v>769677</v>
-      </c>
-      <c r="F11" s="2" t="n">
-        <v>1545458</v>
-      </c>
-      <c r="G11" s="2" t="n">
-        <v>3416487</v>
-      </c>
-      <c r="H11" s="2" t="n">
-        <v>14062908</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>Books</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>Val</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="n">
-        <v>4421317</v>
-      </c>
-      <c r="D12" s="2" t="n">
-        <v>222023</v>
-      </c>
-      <c r="E12" s="2" t="n">
-        <v>158347</v>
-      </c>
-      <c r="F12" s="2" t="n">
-        <v>274448</v>
-      </c>
-      <c r="G12" s="2" t="n">
-        <v>648563</v>
-      </c>
-      <c r="H12" s="2" t="n">
-        <v>3117936</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>Books</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="n">
-        <v>4421318</v>
-      </c>
-      <c r="D13" s="2" t="n">
-        <v>255778</v>
-      </c>
-      <c r="E13" s="2" t="n">
-        <v>152873</v>
-      </c>
-      <c r="F13" s="2" t="n">
-        <v>234151</v>
-      </c>
-      <c r="G13" s="2" t="n">
-        <v>567882</v>
-      </c>
-      <c r="H13" s="2" t="n">
-        <v>3210634</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
